--- a/reports/Итоговый отчёт.xlsx
+++ b/reports/Итоговый отчёт.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
   <si>
     <t>Цель тестирования</t>
   </si>
@@ -152,6 +152,9 @@
   </si>
   <si>
     <t>Шрифт стоит изменить и сделать более чётким и видимым</t>
+  </si>
+  <si>
+    <t>Номер</t>
   </si>
 </sst>
 </file>
@@ -226,7 +229,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -248,21 +251,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -578,14 +590,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="11" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="2">
@@ -593,7 +606,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="11" t="s">
         <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -601,7 +614,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="7" t="s">
@@ -609,7 +622,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B5" t="s">
@@ -617,32 +630,32 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="16"/>
+      <c r="B8" s="14"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>8</v>
       </c>
     </row>
@@ -671,22 +684,24 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="10"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="11" t="s">
         <v>7</v>
       </c>
     </row>
@@ -733,20 +748,20 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -766,8 +781,8 @@
       <c r="A21">
         <v>1</v>
       </c>
-      <c r="B21" t="s">
-        <v>15</v>
+      <c r="B21" s="15" t="s">
+        <v>14</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>43</v>
@@ -808,33 +823,43 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="15"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="C28" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="4">
+        <v>1</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="C29" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>2</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="C30" s="4" t="s">
         <v>45</v>
       </c>
     </row>
@@ -854,11 +879,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A27:B27"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A7:D7"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1"/>

--- a/reports/Итоговый отчёт.xlsx
+++ b/reports/Итоговый отчёт.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t>Цель тестирования</t>
   </si>
@@ -155,6 +155,12 @@
   </si>
   <si>
     <t>Номер</t>
+  </si>
+  <si>
+    <t>1 (4%)</t>
+  </si>
+  <si>
+    <t>26 (96%)</t>
   </si>
 </sst>
 </file>
@@ -229,7 +235,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -255,26 +261,35 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -590,12 +605,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -638,18 +653,18 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="14"/>
+      <c r="B8" s="16"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
@@ -663,7 +678,7 @@
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="20">
         <v>27</v>
       </c>
     </row>
@@ -671,25 +686,25 @@
       <c r="A11" t="s">
         <v>6</v>
       </c>
-      <c r="B11">
-        <v>26</v>
+      <c r="B11" s="20" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
-      <c r="B12">
-        <v>1</v>
+      <c r="B12" s="20" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
@@ -748,12 +763,12 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
@@ -778,16 +793,16 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="A21" s="21">
         <v>1</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="22" t="s">
         <v>42</v>
       </c>
     </row>
@@ -824,11 +839,11 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
